--- a/docs/Part_List.xlsx
+++ b/docs/Part_List.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kees\Documents\NastyThermostat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kees\Documents\GitHub\NastyThermostat\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F424FF28-4AAC-4DDA-97FD-D52193676695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B3BE35-AD6F-4400-B798-7F447647B694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{11FB710B-282E-4353-88E6-4286505DACD9}"/>
+    <workbookView xWindow="345" yWindow="3300" windowWidth="21600" windowHeight="11295" xr2:uid="{11FB710B-282E-4353-88E6-4286505DACD9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Blad1" sheetId="1" r:id="rId1"/>
-    <sheet name="Blad2" sheetId="2" r:id="rId2"/>
+    <sheet name="Part_List" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$J$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Blad2!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Part_List!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
   <si>
     <t>Item No.</t>
   </si>
@@ -53,21 +51,12 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Qty</t>
-  </si>
-  <si>
     <t>Unit Price (€)</t>
   </si>
   <si>
-    <t>Total (€)</t>
-  </si>
-  <si>
     <t>Supplier</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -77,136 +66,22 @@
     <t>ESP32-C6 LCD 1.47</t>
   </si>
   <si>
-    <t>Waveshare ESP32-C6 with ST7789 display</t>
-  </si>
-  <si>
-    <t>28.00</t>
-  </si>
-  <si>
-    <t>Waveshare</t>
-  </si>
-  <si>
-    <t>Installed</t>
-  </si>
-  <si>
     <t>Main controller</t>
   </si>
   <si>
     <t>DRV8825 Stepper Driver</t>
   </si>
   <si>
-    <t>Stepper motor driver module</t>
-  </si>
-  <si>
-    <t>6.00</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Microstepping enabled</t>
-  </si>
-  <si>
     <t>Mechanical</t>
   </si>
   <si>
     <t>NEMA17 Stepper Motor</t>
   </si>
   <si>
-    <t>1.8° step angle</t>
-  </si>
-  <si>
-    <t>18.00</t>
-  </si>
-  <si>
-    <t>AliExpress</t>
-  </si>
-  <si>
-    <t>42mm body</t>
-  </si>
-  <si>
-    <t>GT2 Pulley (20T)</t>
-  </si>
-  <si>
-    <t>20 teeth, 5mm bore</t>
-  </si>
-  <si>
-    <t>4.00</t>
-  </si>
-  <si>
-    <t>On stepper</t>
-  </si>
-  <si>
-    <t>GT2 Pulley (138T)</t>
-  </si>
-  <si>
-    <t>Custom pulley for Nest</t>
-  </si>
-  <si>
-    <t>10.00</t>
-  </si>
-  <si>
-    <t>3D printed</t>
-  </si>
-  <si>
-    <t>Mounted on thermostat</t>
-  </si>
-  <si>
-    <t>Closed loop</t>
-  </si>
-  <si>
-    <t>5.00</t>
-  </si>
-  <si>
-    <t>Main drive belt</t>
-  </si>
-  <si>
-    <t>DS18B20 Sensor</t>
-  </si>
-  <si>
-    <t>Waterproof digital temp sensor</t>
-  </si>
-  <si>
-    <t>3.50</t>
-  </si>
-  <si>
-    <t>GPIO 9</t>
-  </si>
-  <si>
     <t>KY-040 Rotary Encoder</t>
   </si>
   <si>
-    <t>With push button</t>
-  </si>
-  <si>
-    <t>2.50</t>
-  </si>
-  <si>
-    <t>Menu control</t>
-  </si>
-  <si>
     <t>Power</t>
-  </si>
-  <si>
-    <t>DC-DC Converter</t>
-  </si>
-  <si>
-    <t>12V → 5V buck converter</t>
-  </si>
-  <si>
-    <t>Powers ESP</t>
-  </si>
-  <si>
-    <t>12V Power Supply</t>
-  </si>
-  <si>
-    <t>3A</t>
-  </si>
-  <si>
-    <t>12.00</t>
-  </si>
-  <si>
-    <t>System supply</t>
   </si>
   <si>
     <t>GT2 Belt 320mm</t>
@@ -388,7 +263,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="_ [$€-413]\ * #,##0.00_ ;_ [$€-413]\ * \-#,##0.00_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ [$€-413]\ * #,##0.00_ ;_ [$€-413]\ * \-#,##0.00_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -439,13 +314,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -762,387 +637,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7121DA-16E5-4480-8D26-EAFCB794EB8F}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
-    <col min="4" max="4" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J11" xr:uid="{AE7121DA-16E5-4480-8D26-EAFCB794EB8F}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Mechanical"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87CCD5A-47FF-4628-8FFB-7B66E42B7453}">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1170,16 +664,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1187,13 +681,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1202,10 +696,10 @@
         <v>15.89</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1213,13 +707,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1228,10 +722,10 @@
         <v>1.69</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1239,13 +733,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1254,10 +748,10 @@
         <v>1.01</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1265,13 +759,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1280,10 +774,10 @@
         <v>9.76</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1291,13 +785,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1306,10 +800,10 @@
         <v>1.83</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1317,13 +811,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1332,10 +826,10 @@
         <v>1.55</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1343,13 +837,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1358,10 +852,10 @@
         <v>1.89</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1369,13 +863,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="E9" s="4">
         <v>1</v>
@@ -1384,10 +878,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1395,13 +889,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1410,10 +904,10 @@
         <v>11.68</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1421,13 +915,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1436,10 +930,10 @@
         <v>1.89</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1447,13 +941,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1462,10 +956,10 @@
         <v>2.25</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1473,13 +967,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1488,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1499,13 +993,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1514,10 +1008,10 @@
         <v>1.5</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="H14" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1525,13 +1019,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1540,10 +1034,10 @@
         <v>3.29</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="H15" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1551,13 +1045,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1566,10 +1060,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1577,19 +1071,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="E17">
         <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1597,19 +1091,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E18">
         <v>6</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1617,19 +1111,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1637,19 +1131,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1657,19 +1151,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1677,19 +1171,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">

--- a/docs/Part_List.xlsx
+++ b/docs/Part_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kees\Documents\GitHub\NastyThermostat\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B3BE35-AD6F-4400-B798-7F447647B694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B98DE5-089E-4351-82D9-9244D609808E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="3300" windowWidth="21600" windowHeight="11295" xr2:uid="{11FB710B-282E-4353-88E6-4286505DACD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11FB710B-282E-4353-88E6-4286505DACD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Part_List" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
   <si>
     <t>Item No.</t>
   </si>
@@ -256,6 +256,21 @@
   </si>
   <si>
     <t>Amazon/AliExpress</t>
+  </si>
+  <si>
+    <t>Info/Link</t>
+  </si>
+  <si>
+    <t>https://www.waveshare.com/esp32-c6-lcd-1.47.htm</t>
+  </si>
+  <si>
+    <t>Amazon.nl</t>
+  </si>
+  <si>
+    <t>AliExpress</t>
+  </si>
+  <si>
+    <t>https://nastythermostat.cc/3d</t>
   </si>
 </sst>
 </file>
@@ -265,7 +280,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ [$€-413]\ * #,##0.00_ ;_ [$€-413]\ * \-#,##0.00_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +292,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -299,10 +322,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -324,8 +348,13 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -638,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87CCD5A-47FF-4628-8FFB-7B66E42B7453}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -647,10 +676,11 @@
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.85546875" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="8" max="8" width="39.140625" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -673,10 +703,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -698,11 +731,14 @@
       <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -724,11 +760,14 @@
       <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H3" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -750,11 +789,14 @@
       <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -776,11 +818,14 @@
       <c r="G5" t="s">
         <v>23</v>
       </c>
-      <c r="H5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -802,11 +847,14 @@
       <c r="G6" t="s">
         <v>26</v>
       </c>
-      <c r="H6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -828,11 +876,14 @@
       <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="H7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -854,11 +905,14 @@
       <c r="G8" t="s">
         <v>36</v>
       </c>
-      <c r="H8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -880,11 +934,14 @@
       <c r="G9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -906,11 +963,14 @@
       <c r="G10" t="s">
         <v>39</v>
       </c>
-      <c r="H10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -932,11 +992,14 @@
       <c r="G11" t="s">
         <v>42</v>
       </c>
-      <c r="H11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -958,11 +1021,14 @@
       <c r="G12" t="s">
         <v>42</v>
       </c>
-      <c r="H12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -984,11 +1050,11 @@
       <c r="G13" t="s">
         <v>53</v>
       </c>
-      <c r="H13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1010,11 +1076,14 @@
       <c r="G14" t="s">
         <v>54</v>
       </c>
-      <c r="H14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1036,11 +1105,14 @@
       <c r="G15" t="s">
         <v>71</v>
       </c>
-      <c r="H15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H15" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1062,11 +1134,11 @@
       <c r="G16" t="s">
         <v>69</v>
       </c>
-      <c r="H16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1086,7 +1158,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1106,7 +1178,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1126,7 +1198,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1145,8 +1217,11 @@
       <c r="G20" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1165,8 +1240,11 @@
       <c r="G21" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1185,27 +1263,50 @@
       <c r="G22" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C31" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G14" xr:uid="{F87CCD5A-47FF-4628-8FFB-7B66E42B7453}"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{F79AE15B-8240-4395-9DA4-39A1200C4584}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{B1294417-4AC5-4202-A8F6-932BA3642689}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{BD8E1226-78DE-4D58-8ADF-2F784EE49F87}"/>
+    <hyperlink ref="H14" r:id="rId4" xr:uid="{B17F365C-8125-4E88-918E-A20403164C12}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{A05C0B76-1EED-4D1C-BD87-8FE27C2440C7}"/>
+    <hyperlink ref="H4" r:id="rId6" xr:uid="{8AAABDF3-C7BD-4B30-B351-63C38E5A45F1}"/>
+    <hyperlink ref="H3" r:id="rId7" xr:uid="{B462CB55-5494-4CAB-B5E0-27259110CFE4}"/>
+    <hyperlink ref="H7" r:id="rId8" xr:uid="{EC4164E1-CF18-410F-A571-265D103D5D6A}"/>
+    <hyperlink ref="H12" r:id="rId9" xr:uid="{E785BCF3-6988-411D-AA54-8FC5F87E5B16}"/>
+    <hyperlink ref="H8" r:id="rId10" xr:uid="{35BC218B-8ACA-46A6-9C62-6CD0C8250366}"/>
+    <hyperlink ref="I2" r:id="rId11" xr:uid="{BE06F5B0-9118-4358-BED1-0EC23C8959A6}"/>
+    <hyperlink ref="H15" r:id="rId12" xr:uid="{4C9C3615-53FE-4D9D-8FBC-79FDFD8D7E90}"/>
+    <hyperlink ref="H10" r:id="rId13" xr:uid="{FAC00B2D-C1D7-4CB3-8553-45B4240FE22D}"/>
+    <hyperlink ref="H9" r:id="rId14" xr:uid="{D3C788B7-8359-46BC-9809-F7DC59E15A0F}"/>
+    <hyperlink ref="H11" r:id="rId15" xr:uid="{99F0C93A-C798-4EC4-948E-B9A53C55E32B}"/>
+    <hyperlink ref="H20" r:id="rId16" xr:uid="{902FF9DE-A7C0-4013-8D3C-1AC7578BC661}"/>
+    <hyperlink ref="H21" r:id="rId17" xr:uid="{337ED47D-74B7-4E5A-BD1F-D9E50670D909}"/>
+    <hyperlink ref="H22" r:id="rId18" xr:uid="{D8DAAB14-3BB2-4445-A27D-F8CF6E45FD3F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>